--- a/03_test-cases/v1.0/fragments/TC-CANHAN-v1.0.xlsx
+++ b/03_test-cases/v1.0/fragments/TC-CANHAN-v1.0.xlsx
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C18" s="205" t="inlineStr">
         <is>
-          <t>Quan sát thực tế app</t>
+          <t>DOC-v1.0-02 §3.9</t>
         </is>
       </c>
       <c r="D18" s="205" t="inlineStr">
@@ -3573,7 +3573,7 @@
       </c>
       <c r="C19" s="229" t="inlineStr">
         <is>
-          <t>Quan sát thực tế app</t>
+          <t>DOC-v1.0-01 (GIFT-01) + ảnh DOC-v1.0-04</t>
         </is>
       </c>
       <c r="D19" s="229" t="inlineStr">
@@ -3877,7 +3877,7 @@
       </c>
       <c r="C23" s="229" t="inlineStr">
         <is>
-          <t>Quan sát thực tế app</t>
+          <t>Ảnh DOC-v1.0-04 (Quà đã nhận)</t>
         </is>
       </c>
       <c r="D23" s="229" t="inlineStr">
@@ -3983,7 +3983,7 @@
       </c>
       <c r="C24" s="229" t="inlineStr">
         <is>
-          <t>Quan sát thực tế app</t>
+          <t>Ảnh DOC-v1.0-04 (Quà đã nhận)</t>
         </is>
       </c>
       <c r="D24" s="229" t="inlineStr">
@@ -4089,7 +4089,7 @@
       </c>
       <c r="C25" s="205" t="inlineStr">
         <is>
-          <t>Quan sát thực tế app</t>
+          <t>Chờ BA bổ sung</t>
         </is>
       </c>
       <c r="D25" s="205" t="inlineStr">
@@ -4195,7 +4195,7 @@
       </c>
       <c r="C26" s="229" t="inlineStr">
         <is>
-          <t>Quan sát thực tế app</t>
+          <t>Chờ BA bổ sung</t>
         </is>
       </c>
       <c r="D26" s="229" t="inlineStr">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="C27" s="229" t="inlineStr">
         <is>
-          <t>Quan sát thực tế app</t>
+          <t>Chờ BA bổ sung</t>
         </is>
       </c>
       <c r="D27" s="229" t="inlineStr">

--- a/03_test-cases/v1.0/fragments/TC-CANHAN-v1.0.xlsx
+++ b/03_test-cases/v1.0/fragments/TC-CANHAN-v1.0.xlsx
@@ -456,7 +456,7 @@
       <color rgb="FFFFFFFF"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="37">
     <fill>
       <patternFill/>
     </fill>
@@ -665,6 +665,11 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -902,7 +907,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="247">
+  <cellXfs count="248">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -1626,6 +1631,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3593,7 +3599,7 @@
       </c>
       <c r="G19" s="238" t="inlineStr">
         <is>
-          <t>Đã đăng nhập, đang ở màn Cá nhân</t>
+          <t>Đã đăng nhập với vai trò Carrier (chủ sở hữu quà đã nhận), đang ở màn Cá nhân</t>
         </is>
       </c>
       <c r="H19" s="238" t="inlineStr">
@@ -3661,7 +3667,11 @@
         <f>IFERROR(IF($AJ19&lt;&gt;"",$AJ19,IF($AE19&lt;&gt;"",$AE19,IF($Z19&lt;&gt;"",$Z19,IF($U19&lt;&gt;"",$U19,IF($P19&lt;&gt;"",$P19,""))))),"")</f>
         <v/>
       </c>
-      <c r="AP19" s="234" t="n"/>
+      <c r="AP19" s="234" t="inlineStr">
+        <is>
+          <t>Nguồn: merge CA v1.1 `C-GIFT-2` — bug wiring v1.0 (màn "Quà đã nhận" hiện nhầm ở Receiver) đã fix, nay đúng ở Cá nhân của Carrier, khớp Figma</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="60" customHeight="1" s="206">
       <c r="A20" s="229" t="n"/>
@@ -4089,7 +4099,7 @@
       </c>
       <c r="C25" s="205" t="inlineStr">
         <is>
-          <t>Chờ BA bổ sung</t>
+          <t>DOC-v1.0-01 §D1b (US-D20) + quan sát app STG (QA GiangDC2, chat 2026-07-27)</t>
         </is>
       </c>
       <c r="D25" s="205" t="inlineStr">
@@ -4195,7 +4205,7 @@
       </c>
       <c r="C26" s="229" t="inlineStr">
         <is>
-          <t>Chờ BA bổ sung</t>
+          <t>DOC-v1.0-01 §D1b (US-D20) + quan sát app STG (QA GiangDC2, chat 2026-07-27)</t>
         </is>
       </c>
       <c r="D26" s="229" t="inlineStr">
@@ -4301,7 +4311,7 @@
       </c>
       <c r="C27" s="229" t="inlineStr">
         <is>
-          <t>Chờ BA bổ sung</t>
+          <t>DOC-v1.0-01 §D1b (US-D20) + quan sát app STG (QA GiangDC2, chat 2026-07-27)</t>
         </is>
       </c>
       <c r="D27" s="229" t="inlineStr">
@@ -4390,18 +4400,67 @@
       <c r="AP27" s="234" t="n"/>
     </row>
     <row r="28" ht="60" customHeight="1" s="206">
-      <c r="A28" s="229" t="n"/>
-      <c r="B28" s="229" t="n"/>
-      <c r="C28" s="229" t="n"/>
-      <c r="D28" s="229" t="n"/>
-      <c r="E28" s="229" t="n"/>
-      <c r="F28" s="238" t="n"/>
-      <c r="G28" s="238" t="n"/>
-      <c r="H28" s="238" t="n"/>
-      <c r="I28" s="238" t="n"/>
-      <c r="J28" s="229" t="n"/>
-      <c r="K28" s="229" t="n"/>
-      <c r="L28" s="229" t="n"/>
+      <c r="A28" s="229">
+        <f>IF(C28="","",$C$2&amp;"."&amp;COUNTA($C$8:C28)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="B28" s="229" t="inlineStr">
+        <is>
+          <t>REQ-GIFT-001</t>
+        </is>
+      </c>
+      <c r="C28" s="229" t="inlineStr">
+        <is>
+          <t>DOC-v1.0-01 §D1b (US-D20) + quan sát app STG (QA GiangDC2, chat 2026-07-27)</t>
+        </is>
+      </c>
+      <c r="D28" s="229" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="E28" s="229" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F28" s="238" t="inlineStr">
+        <is>
+          <t>Check đầy đủ + đúng 3 thành phần hiển thị tại màn "Quà đã nhận" (trạng thái có dữ liệu)</t>
+        </is>
+      </c>
+      <c r="G28" s="238" t="inlineStr">
+        <is>
+          <t>Carrier đã nhận quà từ ít nhất 2 đơn khác nhau, gồm ≥2 loại quà (màn có dữ liệu)</t>
+        </is>
+      </c>
+      <c r="H28" s="238" t="inlineStr">
+        <is>
+          <t>1. Mở app FoxEco bằng tài khoản Carrier ở Pre-condition
+2. Bấm "Cá nhân" tại bottom nav → bấm menu "Quà đã nhận"
+3. Quan sát toàn bộ màn "Quà đã nhận"</t>
+        </is>
+      </c>
+      <c r="I28" s="238" t="inlineStr">
+        <is>
+          <t>3. Màn hiển thị đủ 3 thành phần của trạng thái CÓ dữ liệu: (1) icon quay lại ở header, (2) card đếm số theo từng loại quà (chỉ loại đã nhận), (3) danh sách lịch sử nhận quà — không thiếu thành phần nào. Thành phần thứ 4 của block (empty state) chỉ xuất hiện khi chưa nhận quà nào, verify riêng tại TC_02.11</t>
+        </is>
+      </c>
+      <c r="J28" s="229" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="K28" s="229" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="L28" s="229" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="M28" s="229" t="n"/>
       <c r="N28" s="231" t="n"/>
       <c r="O28" s="231" t="n"/>
@@ -4428,17 +4487,86 @@
       <c r="AJ28" s="232" t="n"/>
       <c r="AK28" s="232" t="n"/>
       <c r="AL28" s="232" t="n"/>
-      <c r="AM28" s="233" t="n"/>
-      <c r="AN28" s="233" t="n"/>
-      <c r="AO28" s="233" t="n"/>
-      <c r="AP28" s="234" t="n"/>
-    </row>
-    <row r="29" ht="15.75" customHeight="1" s="206">
-      <c r="A29" s="229" t="n"/>
-      <c r="B29" s="236" t="n"/>
-      <c r="J29" s="229" t="n"/>
-      <c r="K29" s="229" t="n"/>
-      <c r="L29" s="229" t="n"/>
+      <c r="AM28" s="233">
+        <f>IF($A28="","",IF(OR($N28="Yes",$S28="Yes",$X28="Yes",$AC28="Yes",$AH28="Yes"),"Yes","No"))</f>
+        <v/>
+      </c>
+      <c r="AN28" s="233">
+        <f>IF($A28="","",IFERROR(IF($AI28&lt;&gt;"",$AI28,IF($AD28&lt;&gt;"",$AD28,IF($Y28&lt;&gt;"",$Y28,IF($T28&lt;&gt;"",$T28,IF($O28&lt;&gt;"",$O28,""))))),""))</f>
+        <v/>
+      </c>
+      <c r="AO28" s="233">
+        <f>IFERROR(IF($AJ28&lt;&gt;"",$AJ28,IF($AE28&lt;&gt;"",$AE28,IF($Z28&lt;&gt;"",$Z28,IF($U28&lt;&gt;"",$U28,IF($P28&lt;&gt;"",$P28,""))))),"")</f>
+        <v/>
+      </c>
+      <c r="AP28" s="234" t="inlineStr">
+        <is>
+          <t>Field/column completeness check — auto-derived (xem generate.md Step 3b) | Bổ sung 2026-07-30 sau finding review-tc **M1 (R2-15)** — trước đó màn "Quà đã nhận" không có TC completeness nào | ⚠ Thành phần "danh sách lịch sử" hiện CHỈ có bằng chứng văn bản (US-D20), chưa có ảnh Figma/app STG đối chiếu → cần vibe-test xác nhận trước khi coi Expected là final (Project_rule §10.1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="60" customHeight="1" s="206">
+      <c r="A29" s="229">
+        <f>IF(C29="","",$C$2&amp;"."&amp;COUNTA($C$8:C29)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="B29" s="229" t="inlineStr">
+        <is>
+          <t>REQ-GIFT-001</t>
+        </is>
+      </c>
+      <c r="C29" s="229" t="inlineStr">
+        <is>
+          <t>DOC-v1.0-01 §D1b (US-D20) + quan sát app STG (QA GiangDC2, chat 2026-07-27)</t>
+        </is>
+      </c>
+      <c r="D29" s="229" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E29" s="229" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F29" s="238" t="inlineStr">
+        <is>
+          <t>Check danh sách lịch sử nhận quà hiển thị đúng các lần đã nhận</t>
+        </is>
+      </c>
+      <c r="G29" s="238" t="inlineStr">
+        <is>
+          <t>Carrier đã nhận ≥2 quà từ ≥2 đơn khác nhau (dữ liệu dàn dựng, biết trước loại quà + người tặng + thời điểm từng lần) — [TBD] điền giá trị khi setup STG</t>
+        </is>
+      </c>
+      <c r="H29" s="238" t="inlineStr">
+        <is>
+          <t>1. Mở app FoxEco bằng tài khoản Carrier ở Pre-condition
+2. Bấm "Cá nhân" tại bottom nav → bấm menu "Quà đã nhận"
+3. Quan sát danh sách lịch sử nhận quà</t>
+        </is>
+      </c>
+      <c r="I29" s="238" t="inlineStr">
+        <is>
+          <t>3. Danh sách lịch sử liệt kê đủ đúng các lần nhận quà như dữ liệu ở Pre-condition (không thiếu lần nào, không trùng lặp), mỗi dòng đối chiếu được với 1 lần tặng thật. Nếu app KHÔNG có danh sách lịch sử trên UI → TC FAIL, mở clarification với BA vì US-D20 nêu rõ "đếm theo loại + lịch sử"</t>
+        </is>
+      </c>
+      <c r="J29" s="229" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="K29" s="229" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="L29" s="229" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="M29" s="229" t="n"/>
       <c r="N29" s="231" t="n"/>
       <c r="O29" s="231" t="n"/>
@@ -4465,10 +4593,23 @@
       <c r="AJ29" s="232" t="n"/>
       <c r="AK29" s="232" t="n"/>
       <c r="AL29" s="232" t="n"/>
-      <c r="AM29" s="233" t="n"/>
-      <c r="AN29" s="233" t="n"/>
-      <c r="AO29" s="233" t="n"/>
-      <c r="AP29" s="234" t="n"/>
+      <c r="AM29" s="233">
+        <f>IF($A29="","",IF(OR($N29="Yes",$S29="Yes",$X29="Yes",$AC29="Yes",$AH29="Yes"),"Yes","No"))</f>
+        <v/>
+      </c>
+      <c r="AN29" s="233">
+        <f>IF($A29="","",IFERROR(IF($AI29&lt;&gt;"",$AI29,IF($AD29&lt;&gt;"",$AD29,IF($Y29&lt;&gt;"",$Y29,IF($T29&lt;&gt;"",$T29,IF($O29&lt;&gt;"",$O29,""))))),""))</f>
+        <v/>
+      </c>
+      <c r="AO29" s="233">
+        <f>IFERROR(IF($AJ29&lt;&gt;"",$AJ29,IF($AE29&lt;&gt;"",$AE29,IF($Z29&lt;&gt;"",$Z29,IF($U29&lt;&gt;"",$U29,IF($P29&lt;&gt;"",$P29,""))))),"")</f>
+        <v/>
+      </c>
+      <c r="AP29" s="234" t="inlineStr">
+        <is>
+          <t>Technique: N/A — baseline (derive trực tiếp từ US-D20, không thuộc rubric B1–B8) | Bổ sung 2026-07-30 sau finding review-tc **M1 (R2-15)** — trước đó thành phần "danh sách lịch sử" 0 TC ở mọi fragment | ⚠ Chỉ có bằng chứng văn bản (US-D20), chưa có ảnh Figma/app STG (Project_rule §10.1) | Cần bổ sung test data trong catalog (fixture lịch sử nhận quà chưa có)</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="60" customHeight="1" s="206">
       <c r="A30" s="229" t="n"/>
@@ -20351,9 +20492,9 @@
           <t>Quan sát thực tế app — 4 loại quà, load có điều kiện</t>
         </is>
       </c>
-      <c r="D8" s="246" t="inlineStr">
-        <is>
-          <t>✅ 1 (all-received, cộng với partial=baseline + none=SC-GIFT-006)</t>
+      <c r="D8" s="247" t="inlineStr">
+        <is>
+          <t>✅ 2 (EP-partial baseline — chỉ load loại đã nhận; EP-all-received — đủ 4/4 loại; partition none=0 quà thuộc SC-GIFT-006)</t>
         </is>
       </c>
       <c r="E8" s="246" t="inlineStr">
@@ -20392,11 +20533,11 @@
         </is>
       </c>
       <c r="L8" s="205" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M8" s="205" t="inlineStr">
         <is>
-          <t>100% (2/2)</t>
+          <t>100% (2/2) — +2 TC baseline (completeness màn + danh sách lịch sử, bổ sung 2026-07-30)</t>
         </is>
       </c>
     </row>
@@ -20605,14 +20746,14 @@
     <row r="14">
       <c r="A14" s="205" t="inlineStr">
         <is>
-          <t>Total TCs (baseline 10 + derived 5): 15</t>
+          <t>Total TCs (baseline 12 + derived 5): 17</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="205" t="inlineStr">
         <is>
-          <t>Most-applied technique: B2 BVA (SC-USR-004: 3, SC-GIFT-003: 1) / B1 EP (SC-GIFT-003: 1)</t>
+          <t>Most-applied technique: B1 EP (SC-USR-004: 0, SC-GIFT-003: 2) / B2 BVA (SC-USR-004: 3, SC-GIFT-003: 1)</t>
         </is>
       </c>
     </row>

--- a/03_test-cases/v1.0/fragments/TC-CANHAN-v1.0.xlsx
+++ b/03_test-cases/v1.0/fragments/TC-CANHAN-v1.0.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Test Cases" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Cá nhân" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Coverage Matrix" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
